--- a/data/dividends_info_20260314.xlsx
+++ b/data/dividends_info_20260314.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K65"/>
+  <dimension ref="A1:K53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2089,11 +2089,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.61</v>
+        <v>0.3</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -2117,14 +2117,14 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>IT0004720733</t>
+          <t>IT0005440893</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>18.3799991607666</v>
+        <v>28</v>
       </c>
       <c r="I36" t="n">
-        <v>3.318824961113642</v>
+        <v>1.071428571428571</v>
       </c>
       <c r="J36" t="n">
         <v>51</v>
@@ -2136,11 +2136,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5105</v>
+        <v>0.16</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -2149,12 +2149,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2164,44 +2164,44 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>IT0001041000</t>
+          <t>IT0001033700</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>8.510000228881836</v>
+        <v>5.78000020980835</v>
       </c>
       <c r="I37" t="n">
-        <v>5.998824750526201</v>
+        <v>2.768165989483679</v>
       </c>
       <c r="J37" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="K37" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.27</v>
+        <v>0.065</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>DOLLARI USA</t>
+          <t>EURO</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2211,30 +2211,30 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>LU2592315662</t>
+          <t>IT0003372205</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>6.949999809265137</v>
+        <v>2.210000038146973</v>
       </c>
       <c r="I38" t="n">
-        <v>3.884892192947393</v>
+        <v>2.941176419820373</v>
       </c>
       <c r="J38" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="K38" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.35</v>
+        <v>0.25</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -2243,12 +2243,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2258,30 +2258,30 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>IT0003850929</t>
+          <t>IT0003365613</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>4.519999980926514</v>
+        <v>7.159999847412109</v>
       </c>
       <c r="I39" t="n">
-        <v>7.743362864533833</v>
+        <v>3.491620186142313</v>
       </c>
       <c r="J39" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="K39" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -2290,45 +2290,45 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Straordinario</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>IT0005252736</t>
+          <t>IT0004998065</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>18.79999923706055</v>
+        <v>6.614999771118164</v>
       </c>
       <c r="I40" t="n">
-        <v>3.989361864023487</v>
+        <v>7.558579248680498</v>
       </c>
       <c r="J40" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="K40" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.43</v>
+        <v>0.54</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -2337,12 +2337,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2352,30 +2352,30 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>IT0003203947</t>
+          <t>IT0005218380</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>10.30000019073486</v>
+        <v>11.43000030517578</v>
       </c>
       <c r="I41" t="n">
-        <v>4.174757204245461</v>
+        <v>4.724409322679326</v>
       </c>
       <c r="J41" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="K41" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -2384,12 +2384,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2399,30 +2399,30 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>IT0005322612</t>
+          <t>NL0015435975</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>3.964999914169312</v>
+        <v>6.176000118255615</v>
       </c>
       <c r="I42" t="n">
-        <v>3.783102225651013</v>
+        <v>1.619170953452711</v>
       </c>
       <c r="J42" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="K42" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.197169</v>
+        <v>0.16</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -2431,12 +2431,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2446,30 +2446,30 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>IT0005455875</t>
+          <t>IT0005215329</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>11.47999954223633</v>
+        <v>9.100000381469727</v>
       </c>
       <c r="I43" t="n">
-        <v>1.717500068485116</v>
+        <v>1.758241684536706</v>
       </c>
       <c r="J43" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="K43" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1.1</v>
+        <v>1.36</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -2478,12 +2478,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2493,30 +2493,30 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>IT0005253205</t>
+          <t>IT0005144784</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>25.25</v>
+        <v>26.39999961853027</v>
       </c>
       <c r="I44" t="n">
-        <v>4.356435643564357</v>
+        <v>5.151515225952543</v>
       </c>
       <c r="J44" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="K44" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.38</v>
+        <v>0.585</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -2525,12 +2525,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2540,30 +2540,30 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>IT0001018362</t>
+          <t>IT0004931058</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>10.25</v>
+        <v>12.86999988555908</v>
       </c>
       <c r="I45" t="n">
-        <v>3.707317073170731</v>
+        <v>4.545454585873038</v>
       </c>
       <c r="J45" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="K45" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -2572,12 +2572,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2587,30 +2587,30 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>IT0005440893</t>
+          <t>IT0004176001</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>28</v>
+        <v>98.41999816894531</v>
       </c>
       <c r="I46" t="n">
-        <v>1.071428571428571</v>
+        <v>0.914448299882187</v>
       </c>
       <c r="J46" t="n">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="K46" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.16</v>
+        <v>1.7208</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2619,12 +2619,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2634,30 +2634,30 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>IT0001033700</t>
+          <t>IT0005239360</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>5.78000020980835</v>
+        <v>63.5</v>
       </c>
       <c r="I47" t="n">
-        <v>2.768165989483679</v>
+        <v>2.70992125984252</v>
       </c>
       <c r="J47" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="K47" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>I.CO.P. S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.065</v>
+        <v>0.14</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2681,30 +2681,30 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>IT0003372205</t>
+          <t>IT0001214433</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>2.210000038146973</v>
+        <v>22.20000076293945</v>
       </c>
       <c r="I48" t="n">
-        <v>2.941176419820373</v>
+        <v>0.6306306089579743</v>
       </c>
       <c r="J48" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="K48" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.25</v>
+        <v>0.06</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2713,12 +2713,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2728,30 +2728,30 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>IT0003365613</t>
+          <t>IT0005418204</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>7.159999847412109</v>
+        <v>1.509999990463257</v>
       </c>
       <c r="I49" t="n">
-        <v>3.491620186142313</v>
+        <v>3.973509958870426</v>
       </c>
       <c r="J49" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="K49" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>Confinvest F.L. S.p.A.</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5</v>
+        <v>0.034</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2775,30 +2775,30 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>IT0004998065</t>
+          <t>IT0005379604</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>6.614999771118164</v>
+        <v>1.929999947547913</v>
       </c>
       <c r="I50" t="n">
-        <v>7.558579248680498</v>
+        <v>1.7616580789651</v>
       </c>
       <c r="J50" t="n">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="K50" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.54</v>
+        <v>0.26</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -2807,92 +2807,92 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Interim</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>IT0005218380</t>
+          <t>IT0003132476</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>11.43000030517578</v>
+        <v>22.35000038146973</v>
       </c>
       <c r="I51" t="n">
-        <v>4.724409322679326</v>
+        <v>1.163310942113293</v>
       </c>
       <c r="J51" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="K51" t="n">
-        <v>39</v>
+        <v>11</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>EURO</t>
+          <t>DOLLARI USA</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Interim</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>NL0015435975</t>
+          <t>NL0000226223</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>6.176000118255615</v>
+        <v>28.61499977111816</v>
       </c>
       <c r="I52" t="n">
-        <v>1.619170953452711</v>
+        <v>0.3145203589721474</v>
       </c>
       <c r="J52" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="K52" t="n">
-        <v>39</v>
+        <v>11</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.16</v>
+        <v>0.65</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2901,598 +2901,34 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Interim</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>IT0005215329</t>
+          <t>IT0001031084</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>9.100000381469727</v>
+        <v>50.29999923706055</v>
       </c>
       <c r="I53" t="n">
-        <v>1.758241684536706</v>
+        <v>1.292246540475266</v>
       </c>
       <c r="J53" t="n">
-        <v>37</v>
+        <v>-19</v>
       </c>
       <c r="K53" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Ferrari N.V.</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>3.615</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>NL0011585146</t>
-        </is>
-      </c>
-      <c r="H54" t="n">
-        <v>289.2000122070312</v>
-      </c>
-      <c r="I54" t="n">
-        <v>1.249999947237938</v>
-      </c>
-      <c r="J54" t="n">
-        <v>37</v>
-      </c>
-      <c r="K54" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Generalfinance S.p.A.</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>IT0005144784</t>
-        </is>
-      </c>
-      <c r="H55" t="n">
-        <v>26.39999961853027</v>
-      </c>
-      <c r="I55" t="n">
-        <v>5.151515225952543</v>
-      </c>
-      <c r="J55" t="n">
-        <v>37</v>
-      </c>
-      <c r="K55" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>MAIRE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>IT0004931058</t>
-        </is>
-      </c>
-      <c r="H56" t="n">
-        <v>12.86999988555908</v>
-      </c>
-      <c r="I56" t="n">
-        <v>4.545454585873038</v>
-      </c>
-      <c r="J56" t="n">
-        <v>37</v>
-      </c>
-      <c r="K56" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>IT0000062957</t>
-        </is>
-      </c>
-      <c r="H57" t="n">
-        <v>15.77000045776367</v>
-      </c>
-      <c r="I57" t="n">
-        <v>3.994926960765223</v>
-      </c>
-      <c r="J57" t="n">
-        <v>37</v>
-      </c>
-      <c r="K57" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Prysmian S.p.A.</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>IT0004176001</t>
-        </is>
-      </c>
-      <c r="H58" t="n">
-        <v>98.41999816894531</v>
-      </c>
-      <c r="I58" t="n">
-        <v>0.914448299882187</v>
-      </c>
-      <c r="J58" t="n">
-        <v>37</v>
-      </c>
-      <c r="K58" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Unicredit S.p.A.</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>1.7208</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>IT0005239360</t>
-        </is>
-      </c>
-      <c r="H59" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="I59" t="n">
-        <v>2.70992125984252</v>
-      </c>
-      <c r="J59" t="n">
-        <v>37</v>
-      </c>
-      <c r="K59" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>I.CO.P. S.p.A. Società Benefit</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>IT0001214433</t>
-        </is>
-      </c>
-      <c r="H60" t="n">
-        <v>22.20000076293945</v>
-      </c>
-      <c r="I60" t="n">
-        <v>0.6306306089579743</v>
-      </c>
-      <c r="J60" t="n">
-        <v>30</v>
-      </c>
-      <c r="K60" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Reti S.p.A.</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>IT0005418204</t>
-        </is>
-      </c>
-      <c r="H61" t="n">
-        <v>1.509999990463257</v>
-      </c>
-      <c r="I61" t="n">
-        <v>3.973509958870426</v>
-      </c>
-      <c r="J61" t="n">
-        <v>30</v>
-      </c>
-      <c r="K61" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Confinvest F.L. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>IT0005379604</t>
-        </is>
-      </c>
-      <c r="H62" t="n">
-        <v>1.929999947547913</v>
-      </c>
-      <c r="I62" t="n">
-        <v>1.7616580789651</v>
-      </c>
-      <c r="J62" t="n">
-        <v>16</v>
-      </c>
-      <c r="K62" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Eni S.p.A.</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Interim</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>IT0003132476</t>
-        </is>
-      </c>
-      <c r="H63" t="n">
-        <v>22.35000038146973</v>
-      </c>
-      <c r="I63" t="n">
-        <v>1.163310942113293</v>
-      </c>
-      <c r="J63" t="n">
-        <v>9</v>
-      </c>
-      <c r="K63" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>STMicroelectronics N.V.</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>DOLLARI USA</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Interim</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>NL0000226223</t>
-        </is>
-      </c>
-      <c r="H64" t="n">
-        <v>28.61499977111816</v>
-      </c>
-      <c r="I64" t="n">
-        <v>0.3145203589721474</v>
-      </c>
-      <c r="J64" t="n">
-        <v>9</v>
-      </c>
-      <c r="K64" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Banca Generali S.p.A.</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Interim</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>IT0001031084</t>
-        </is>
-      </c>
-      <c r="H65" t="n">
-        <v>50.29999923706055</v>
-      </c>
-      <c r="I65" t="n">
-        <v>1.292246540475266</v>
-      </c>
-      <c r="J65" t="n">
-        <v>-19</v>
-      </c>
-      <c r="K65" t="n">
         <v>-17</v>
       </c>
     </row>
@@ -3507,7 +2943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C298"/>
+  <dimension ref="A1:C308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3564,7 +3000,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3574,14 +3010,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3591,14 +3027,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3608,14 +3044,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3625,14 +3061,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3649,7 +3085,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3683,7 +3119,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3836,7 +3272,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3846,14 +3282,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3863,14 +3299,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4091,7 +3527,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4108,7 +3544,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4193,7 +3629,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4210,7 +3646,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4227,7 +3663,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4244,7 +3680,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4254,14 +3690,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4278,7 +3714,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4288,14 +3724,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4305,14 +3741,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4322,7 +3758,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -4346,7 +3782,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4363,7 +3799,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4373,14 +3809,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4390,7 +3826,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4407,14 +3843,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4431,7 +3867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4448,7 +3884,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4458,7 +3894,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4475,14 +3911,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4499,7 +3935,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4509,14 +3945,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>gAIn360 S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4533,7 +3969,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Telesia S.p.A.</t>
+          <t>gAIn360 S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4550,7 +3986,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>Telesia S.p.A.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4560,14 +3996,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>NEXT RE SIIQ S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4577,14 +4013,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>NEXT RE SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4686,7 +4122,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4703,7 +4139,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4720,7 +4156,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4737,7 +4173,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4764,14 +4200,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4788,7 +4224,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -4805,7 +4241,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4822,7 +4258,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -4839,7 +4275,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -4856,7 +4292,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -4866,14 +4302,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -4890,7 +4326,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -4907,7 +4343,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Friends S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -4958,7 +4394,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Antares Vision S.p.A.</t>
+          <t>Friends S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -4975,7 +4411,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>Antares Vision S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -4992,7 +4428,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5026,7 +4462,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5043,7 +4479,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5060,7 +4496,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -5077,7 +4513,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -5094,7 +4530,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -5111,7 +4547,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -5128,7 +4564,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -5138,14 +4574,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -5155,14 +4591,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -5172,7 +4608,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -5189,14 +4625,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -5213,7 +4649,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -5230,7 +4666,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -5247,7 +4683,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -5264,7 +4700,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>Allcore S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -5281,7 +4717,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -5291,14 +4727,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Egomnia S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -5308,14 +4744,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>Egomnia S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -5332,7 +4768,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -5349,7 +4785,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -5366,7 +4802,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Braga Moro Sistemi di Energia S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -5383,7 +4819,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Allcore S.p.A.</t>
+          <t>Braga Moro Sistemi di Energia S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -5417,7 +4853,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -5468,7 +4904,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -5478,14 +4914,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -5502,7 +4938,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -5519,7 +4955,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -5536,7 +4972,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5546,14 +4982,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>rino petino S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5570,7 +5006,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5580,14 +5016,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>rino petino S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5604,7 +5040,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ELSA Solutions S.p.A.</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5621,7 +5057,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Somec S.p.A.</t>
+          <t>DANIELI &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5631,14 +5067,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ATON Green Storage S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5655,7 +5091,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
+          <t>ATON Green Storage S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5665,14 +5101,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Confinvest F.L. S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5689,7 +5125,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>CULTI Milano S.p.A.</t>
+          <t>ELSA Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -5706,7 +5142,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -5716,14 +5152,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>Confinvest F.L. S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -5740,7 +5176,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>CULTI Milano S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -5757,7 +5193,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>CREACTIVES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -5774,7 +5210,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -5791,7 +5227,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5801,14 +5237,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5825,7 +5261,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>KME Group S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5842,7 +5278,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Grifal S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5859,7 +5295,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5869,7 +5305,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5329,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5903,14 +5339,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Grifal S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5927,7 +5363,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>KME Group S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5944,7 +5380,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Lindbergh S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5961,7 +5397,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5978,7 +5414,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5988,14 +5424,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -6005,14 +5441,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6029,7 +5465,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6046,7 +5482,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>RES S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6063,7 +5499,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6080,7 +5516,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6090,14 +5526,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -6107,14 +5543,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -6131,7 +5567,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -6141,14 +5577,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>Lindbergh S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -6158,14 +5594,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>RES S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -6182,7 +5618,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -6199,7 +5635,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -6216,7 +5652,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -6226,14 +5662,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -6250,12 +5686,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -6267,12 +5703,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -6284,7 +5720,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -6301,7 +5737,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>ELES S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -6318,7 +5754,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -6335,7 +5771,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -6352,7 +5788,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -6369,7 +5805,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -6379,14 +5815,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -6403,7 +5839,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -6420,7 +5856,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -6437,7 +5873,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -6454,7 +5890,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -6464,14 +5900,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -6488,7 +5924,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -6505,7 +5941,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -6522,7 +5958,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -6539,7 +5975,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -6549,14 +5985,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -6573,7 +6009,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -6590,7 +6026,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -6607,7 +6043,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -6624,7 +6060,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -6641,7 +6077,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -6658,7 +6094,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>YOLO GROUP S.p.A.</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -6675,7 +6111,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -6692,7 +6128,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -6709,7 +6145,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -6726,46 +6162,46 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6777,12 +6213,12 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -6794,12 +6230,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -6811,12 +6247,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -6828,12 +6264,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -6845,12 +6281,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -6862,12 +6298,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -6879,12 +6315,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>YOLO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -6896,7 +6332,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -6913,7 +6349,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -6930,7 +6366,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>HEALTH ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -6947,7 +6383,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -6957,14 +6393,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -6981,7 +6417,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -6998,7 +6434,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -7015,7 +6451,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -7025,14 +6461,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -7049,7 +6485,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -7066,7 +6502,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -7083,7 +6519,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -7100,7 +6536,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -7117,7 +6553,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -7134,7 +6570,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -7144,14 +6580,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Annual Preliminary Results</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -7168,7 +6604,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -7185,7 +6621,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -7202,7 +6638,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -7219,7 +6655,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -7229,14 +6665,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -7253,7 +6689,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -7270,7 +6706,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -7287,7 +6723,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -7304,7 +6740,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -7321,7 +6757,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -7338,7 +6774,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>HEALTH ITALIA S.p.A.</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -7355,7 +6791,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -7372,7 +6808,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -7389,7 +6825,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -7406,7 +6842,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -7423,7 +6859,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -7440,7 +6876,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -7450,14 +6886,14 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -7474,7 +6910,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -7491,7 +6927,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -7501,14 +6937,14 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -7525,7 +6961,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -7542,7 +6978,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -7559,7 +6995,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -7576,7 +7012,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -7586,14 +7022,14 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -7610,7 +7046,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -7620,19 +7056,19 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -7644,12 +7080,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -7661,12 +7097,12 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -7678,12 +7114,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -7695,12 +7131,12 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -7712,12 +7148,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -7729,12 +7165,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -7746,12 +7182,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -7763,29 +7199,29 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -7797,7 +7233,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -7807,14 +7243,14 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -7831,7 +7267,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -7841,14 +7277,14 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -7865,7 +7301,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -7875,14 +7311,14 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -7892,14 +7328,14 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -7909,14 +7345,14 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -7933,7 +7369,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>Vivenda Group S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -7950,7 +7386,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -7967,7 +7403,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -7984,7 +7420,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -8001,7 +7437,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -8018,7 +7454,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -8028,14 +7464,14 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -8052,7 +7488,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -8069,7 +7505,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>NEUROSOFT</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -8086,7 +7522,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -8096,14 +7532,14 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -8120,7 +7556,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -8137,7 +7573,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -8154,7 +7590,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -8171,7 +7607,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -8188,7 +7624,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -8198,14 +7634,14 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -8222,7 +7658,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -8239,7 +7675,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -8256,46 +7692,46 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -8307,80 +7743,80 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>I.CO.P. S.p.A. Società Benefit</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>NEUROSOFT</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -8392,63 +7828,63 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>BRUNELLO CUCINELLI S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Gas Plus S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -8460,12 +7896,12 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Gas Plus S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -8477,29 +7913,29 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>I.CO.P. S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -8511,12 +7947,12 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -8528,51 +7964,221 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Masi Agricola S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>RT&amp;L S.P.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
+          <t>BORGOSESIA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>BRUNELLO CUCINELLI S.p.A.</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Gas Plus S.p.A.</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Gas Plus S.p.A.</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Analyst Presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Masi Agricola S.p.A.</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>DESTINATION ITALIA S.p.A.</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Generalfinance S.p.A.</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
           <t>Indel B S.p.A.</t>
         </is>
       </c>
-      <c r="B298" t="inlineStr">
+      <c r="B306" t="inlineStr">
         <is>
           <t>2026-04-10</t>
         </is>
       </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Bod Annual Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>RT&amp;L S.P.A.</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Annual General Meeting</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Growens S.p.A.</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
